--- a/artfynd/A 53849-2025 artfynd.xlsx
+++ b/artfynd/A 53849-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1036,6 +1036,470 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130066196</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norra udden A 53846,  Norra udden A 53846, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>565271</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6438303</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130065665</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Blåvikshagen A 53849, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>565182</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6438219</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130065696</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58111</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Blåvikshagen A 53849, Blåvikshagen A 53849, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>565182</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6438240</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130065892</v>
+      </c>
+      <c r="B8" t="n">
+        <v>110747</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Blåvikshagen, Blåvikshagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>565271</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6438303</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53849-2025 artfynd.xlsx
+++ b/artfynd/A 53849-2025 artfynd.xlsx
@@ -1389,7 +1389,7 @@
         <v>130065892</v>
       </c>
       <c r="B8" t="n">
-        <v>110747</v>
+        <v>110760</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1424,6 +1424,9 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blåvikshagen, Blåvikshagen, Sm</t>
@@ -1484,6 +1487,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53849-2025 artfynd.xlsx
+++ b/artfynd/A 53849-2025 artfynd.xlsx
@@ -1041,7 +1041,7 @@
         <v>130066196</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>130065696</v>
       </c>
       <c r="B7" t="n">
-        <v>58111</v>
+        <v>58112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2025 artfynd.xlsx
+++ b/artfynd/A 53849-2025 artfynd.xlsx
@@ -1389,7 +1389,7 @@
         <v>130065892</v>
       </c>
       <c r="B8" t="n">
-        <v>110776</v>
+        <v>110779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2025 artfynd.xlsx
+++ b/artfynd/A 53849-2025 artfynd.xlsx
@@ -1041,7 +1041,7 @@
         <v>130066196</v>
       </c>
       <c r="B5" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>130065665</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>130065696</v>
       </c>
       <c r="B7" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>130065892</v>
       </c>
       <c r="B8" t="n">
-        <v>110779</v>
+        <v>110866</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 53849-2025 artfynd.xlsx
+++ b/artfynd/A 53849-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>7120891</v>
       </c>
       <c r="B2" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565201.1523053104</v>
+        <v>565201</v>
       </c>
       <c r="R2" t="n">
-        <v>6438226.006384764</v>
+        <v>6438226</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2011-11-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-11-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7118591</v>
+        <v>130065665</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,41 +792,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mosshult, Sm</t>
+          <t>Blåvikshagen A 53849, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565201.1523053104</v>
+        <v>565182</v>
       </c>
       <c r="R3" t="n">
-        <v>6438226.006384764</v>
+        <v>6438219</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,27 +855,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-11-01</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-11-01</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Sveaskogs Naturvärdesbedömning -Inventerare: Mille Fagerström  ID;32779</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,27 +885,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7126429</v>
+        <v>130065696</v>
       </c>
       <c r="B4" t="n">
-        <v>107997</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219677</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -955,16 +930,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mosshult, Sm</t>
+          <t>Blåvikshagen A 53849, Blåvikshagen A 53849, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565201.1523053104</v>
+        <v>565182</v>
       </c>
       <c r="R4" t="n">
-        <v>6438226.006384764</v>
+        <v>6438240</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,27 +971,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2011-11-01</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2011-11-01</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;32780</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,12 +1001,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Björn Stenberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1041,7 +1016,7 @@
         <v>130066196</v>
       </c>
       <c r="B5" t="n">
-        <v>57985</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,32 +1129,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130065665</v>
+        <v>7126429</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>111176</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>219677</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1187,24 +1162,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blåvikshagen A 53849, Sm</t>
+          <t>Mosshult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>565182</v>
+        <v>565201</v>
       </c>
       <c r="R6" t="n">
-        <v>6438219</v>
+        <v>6438226</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,22 +1198,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>10:21</t>
+          <t>2011-11-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>10:21</t>
+          <t>2011-11-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;32780</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,22 +1223,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130065696</v>
+        <v>130065892</v>
       </c>
       <c r="B7" t="n">
-        <v>58198</v>
+        <v>111175</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,43 +1246,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>219677</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Blåvikshagen A 53849, Blåvikshagen A 53849, Sm</t>
+          <t>Blåvikshagen, Blåvikshagen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>565182</v>
+        <v>565271</v>
       </c>
       <c r="R7" t="n">
-        <v>6438240</v>
+        <v>6438303</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,6 +1336,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1386,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130065892</v>
+        <v>7118591</v>
       </c>
       <c r="B8" t="n">
-        <v>110866</v>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,46 +1366,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Blåvikshagen, Blåvikshagen, Sm</t>
+          <t>Mosshult, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>565271</v>
+        <v>565201</v>
       </c>
       <c r="R8" t="n">
-        <v>6438303</v>
+        <v>6438226</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1463,22 +1424,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:37</t>
+          <t>2011-11-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:37</t>
+          <t>2011-11-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Sveaskogs Naturvärdesbedömning -Inventerare: Mille Fagerström  ID;32779</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,19 +1443,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
